--- a/Excel_Data/PD220/XF Real-Time ATP Rate Assay PD220,LV,HEALTHY 12.13.25 WITH NORMALIZATION-XF ATP Rate Assay-ATP Production (Basal Rates) (1).xlsx
+++ b/Excel_Data/PD220/XF Real-Time ATP Rate Assay PD220,LV,HEALTHY 12.13.25 WITH NORMALIZATION-XF ATP Rate Assay-ATP Production (Basal Rates) (1).xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leonardharris/PycharmProjects/FA_Metabolism/Excel_Data/PD220/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F93359E-B3A5-A24E-9767-04A35C35EF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="1000" windowWidth="15000" windowHeight="10000"/>
+    <workbookView xWindow="-35180" yWindow="8160" windowWidth="15000" windowHeight="10000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ATP Production (Basal Rates)" sheetId="1" r:id="rId1"/>
@@ -49,9 +55,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>XF Real-Time ATP Rate Assay PD220,LV,HEALTHY 12.13.2025 WITH NORMALIZATION</t>
-  </si>
-  <si>
     <t>True</t>
   </si>
   <si>
@@ -140,26 +143,29 @@
   </si>
   <si>
     <t>glycoATP Production Rate</t>
+  </si>
+  <si>
+    <t>XF Real-Time ATP Rate Assay PD220,LV,HEALTHY 12.13.25 WITH NORMALIZATION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -172,7 +178,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border outline="0">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -183,13 +189,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" relativeIndent="0" readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -197,6 +202,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -484,380 +497,376 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625"/>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="28.5" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="28.5" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>9.18487575659233</v>
       </c>
-      <c r="D10" s="3">
-        <v>17.302603437177</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="D10" s="2">
+        <v>17.302603437177002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="3">
-        <v>6.02805699746747</v>
-      </c>
-      <c r="D11" s="3">
-        <v>11.5123465420519</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="C11" s="2">
+        <v>6.0280569974674698</v>
+      </c>
+      <c r="D11" s="2">
+        <v>11.512346542051899</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <v>6.4192857920614799</v>
+      </c>
+      <c r="D12" s="2">
+        <v>13.034625119182801</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="3">
-        <v>6.41928579206148</v>
-      </c>
-      <c r="D12" s="3">
-        <v>13.0346251191828</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="C13" s="2">
+        <v>7.73648054024176</v>
+      </c>
+      <c r="D13" s="2">
+        <v>10.9581843678995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2">
+        <v>7.5658565338182999</v>
+      </c>
+      <c r="D14" s="2">
+        <v>14.960825483123299</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2">
+        <v>5.8513425550157798</v>
+      </c>
+      <c r="D15" s="2">
+        <v>12.4836364459025</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2">
+        <v>6.3247816447985397</v>
+      </c>
+      <c r="D16" s="2">
+        <v>13.5617960307367</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>5.2155803297536103</v>
+      </c>
+      <c r="D17" s="2">
+        <v>9.6032171876224801</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4.9554098728110301</v>
+      </c>
+      <c r="D18" s="2">
+        <v>12.6889531753291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="3">
-        <v>7.73648054024176</v>
-      </c>
-      <c r="D13" s="3">
-        <v>10.9581843678995</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="3">
-        <v>7.5658565338183</v>
-      </c>
-      <c r="D14" s="3">
-        <v>14.9608254831233</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="C19" s="2">
+        <v>5.26050163484976</v>
+      </c>
+      <c r="D19" s="2">
+        <v>13.661517437841701</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="3">
-        <v>5.85134255501578</v>
-      </c>
-      <c r="D15" s="3">
-        <v>12.4836364459025</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="C20" s="2">
+        <v>7.4214547350737199</v>
+      </c>
+      <c r="D20" s="2">
+        <v>13.5503432538351</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="3">
-        <v>6.32478164479854</v>
-      </c>
-      <c r="D16" s="3">
-        <v>13.5617960307367</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="C21" s="2">
+        <v>4.3671426386998604</v>
+      </c>
+      <c r="D21" s="2">
+        <v>13.270825859039199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5.21558032975361</v>
-      </c>
-      <c r="D17" s="3">
-        <v>9.60321718762248</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="3">
-        <v>4.95540987281103</v>
-      </c>
-      <c r="D18" s="3">
-        <v>12.6889531753291</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3.33634047169308</v>
+      </c>
+      <c r="D22" s="2">
+        <v>12.7331790353121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2.9208420052274602</v>
+      </c>
+      <c r="D23" s="2">
+        <v>20.539645865372901</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="3">
-        <v>5.26050163484976</v>
-      </c>
-      <c r="D19" s="3">
-        <v>13.6615174378417</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="C24" s="2">
+        <v>2.5920170716400599</v>
+      </c>
+      <c r="D24" s="2">
+        <v>15.8068179533846</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3.2017003254249001</v>
+      </c>
+      <c r="D25" s="2">
+        <v>19.085694909986302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="3">
-        <v>7.42145473507372</v>
-      </c>
-      <c r="D20" s="3">
-        <v>13.5503432538351</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="3">
-        <v>4.36714263869986</v>
-      </c>
-      <c r="D21" s="3">
-        <v>13.2708258590392</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="C26" s="2">
+        <v>4.1212544714339403</v>
+      </c>
+      <c r="D26" s="2">
+        <v>18.901517322116501</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3.3950754374901599</v>
+      </c>
+      <c r="D27" s="2">
+        <v>20.807615393228399</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="3">
-        <v>3.33634047169308</v>
-      </c>
-      <c r="D22" s="3">
-        <v>12.7331790353121</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="3">
-        <v>2.92084200522746</v>
-      </c>
-      <c r="D23" s="3">
-        <v>20.5396458653729</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="3">
-        <v>2.59201707164006</v>
-      </c>
-      <c r="D24" s="3">
-        <v>15.8068179533846</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="3">
-        <v>3.2017003254249</v>
-      </c>
-      <c r="D25" s="3">
-        <v>19.0856949099863</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="3">
-        <v>4.12125447143394</v>
-      </c>
-      <c r="D26" s="3">
-        <v>18.9015173221165</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="3">
-        <v>3.39507543749016</v>
-      </c>
-      <c r="D27" s="3">
-        <v>20.8076153932284</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="2">
+        <v>3.1030343019531301</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20.024951084711901</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="3">
-        <v>3.10303430195313</v>
-      </c>
-      <c r="D28" s="3">
-        <v>20.0249510847119</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="3">
-        <v>3.15620950446835</v>
-      </c>
-      <c r="D29" s="3">
-        <v>21.9358178754671</v>
+      <c r="C29" s="2">
+        <v>3.1562095044683498</v>
+      </c>
+      <c r="D29" s="2">
+        <v>21.935817875467102</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection/>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>